--- a/Results/betareg_sensitivity_general_excel.xlsx
+++ b/Results/betareg_sensitivity_general_excel.xlsx
@@ -8,37 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Desktop\Artigos_coauthor\Iberian_plants\Extinction_dynamics_Iberic\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B48583-2206-4E88-A02B-79CD8BC50A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C67F2E-5FF3-4353-A1F7-1B4089C7E854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>mean_estimate</t>
-  </si>
-  <si>
-    <t>sd_estimate</t>
-  </si>
-  <si>
-    <t>mean_p</t>
-  </si>
-  <si>
-    <t>prop_significant</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="16">
   <si>
     <t>Intercept</t>
   </si>
@@ -62,13 +44,40 @@
   </si>
   <si>
     <t>Peninsula</t>
+  </si>
+  <si>
+    <t>Ex. scenario</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Mean estimate</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Significant (%)</t>
+  </si>
+  <si>
+    <t>&lt; 0.001</t>
+  </si>
+  <si>
+    <t>Andalusia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +92,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,16 +127,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,387 +451,392 @@
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>-1.8264302078322401</v>
+      </c>
+      <c r="E2" s="4">
+        <v>6.7534701178998416E-2</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <v>6.3057978630394152E-3</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.117920469254665E-3</v>
+      </c>
+      <c r="F3" s="4">
+        <v>3.1582361622425073E-2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <v>-0.1020174374362901</v>
+      </c>
+      <c r="E4" s="4">
+        <v>5.9196836507810047E-2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.58977475609576013</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>-1.843863812589976</v>
+      </c>
+      <c r="E5" s="4">
+        <v>6.6668951669805451E-2</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1.0765314364585211E-2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1.88370094272728E-3</v>
+      </c>
+      <c r="F6" s="4">
+        <v>8.0037877582814276E-2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4">
+        <v>-8.2850216945780236E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>5.9449770348962587E-2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.66755299630853759</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>-1.8714994281951369</v>
+      </c>
+      <c r="E8" s="4">
+        <v>6.8433543598562796E-2</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D9" s="4">
+        <v>2.0072682135024261E-2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3.9063632028670976E-3</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.1237624564699816</v>
+      </c>
+      <c r="G9" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>-1.8264302078322401</v>
-      </c>
-      <c r="E2">
-        <v>6.7534701178998416E-2</v>
-      </c>
-      <c r="F2">
-        <v>1.2645966930390041E-136</v>
-      </c>
-      <c r="G2">
+      <c r="D10" s="4">
+        <v>-5.806665602821981E-2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>6.3201866082670879E-2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.74441119768251451</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>6.3057978630394152E-3</v>
-      </c>
-      <c r="E3">
-        <v>1.117920469254665E-3</v>
-      </c>
-      <c r="F3">
-        <v>3.1582361622425073E-2</v>
-      </c>
-      <c r="G3">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>-0.1020174374362901</v>
-      </c>
-      <c r="E4">
-        <v>5.9196836507810047E-2</v>
-      </c>
-      <c r="F4">
-        <v>0.58977475609576013</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>-1.843863812589976</v>
-      </c>
-      <c r="E5">
-        <v>6.6668951669805451E-2</v>
-      </c>
-      <c r="F5">
-        <v>1.6147798375161149E-92</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>1.0765314364585211E-2</v>
-      </c>
-      <c r="E6">
-        <v>1.88370094272728E-3</v>
-      </c>
-      <c r="F6">
-        <v>8.0037877582814276E-2</v>
-      </c>
-      <c r="G6">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>-8.2850216945780236E-2</v>
-      </c>
-      <c r="E7">
-        <v>5.9449770348962587E-2</v>
-      </c>
-      <c r="F7">
-        <v>0.66755299630853759</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>-1.8714994281951369</v>
-      </c>
-      <c r="E8">
-        <v>6.8433543598562796E-2</v>
-      </c>
-      <c r="F8">
-        <v>2.8928287506145221E-60</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>2.0072682135024261E-2</v>
-      </c>
-      <c r="E9">
-        <v>3.9063632028670976E-3</v>
-      </c>
-      <c r="F9">
-        <v>0.1237624564699816</v>
-      </c>
-      <c r="G9">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>-5.806665602821981E-2</v>
-      </c>
-      <c r="E10">
-        <v>6.3201866082670879E-2</v>
-      </c>
-      <c r="F10">
-        <v>0.74441119768251451</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
         <v>-1.9629544556285909</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>8.213915685202311E-2</v>
       </c>
-      <c r="F11">
-        <v>6.0686443408429846E-132</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="F11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="4">
         <v>5.8747239580919913E-3</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>1.18928558933025E-3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="4">
         <v>6.8839041954419616E-2</v>
       </c>
-      <c r="G12">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="G12" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
         <v>-0.14174357294838061</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>7.0888968036929817E-2</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="4">
         <v>0.4724344926118344</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
         <v>-1.983953304588429</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>8.1540784190379384E-2</v>
       </c>
-      <c r="F14">
-        <v>2.9120308232946262E-91</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="F14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4">
         <v>1.0402956222417241E-2</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>2.4001371689628469E-3</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4">
         <v>0.1251867673252082</v>
       </c>
-      <c r="G15">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="G15" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
         <v>-0.1163986527464456</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>7.3162058167370522E-2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="4">
         <v>0.56703688292415488</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
         <v>-2.001494394335019</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>8.4895558628605469E-2</v>
       </c>
-      <c r="F17">
-        <v>1.0194919348675301E-59</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="F17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
         <v>1.8164057839875469E-2</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>4.8146255054472781E-3</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="4">
         <v>0.20082851608872099</v>
       </c>
-      <c r="G18">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="G18" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
         <v>-0.1029731534726087</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>7.6188729974503738E-2</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="4">
         <v>0.62841731552282099</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>0</v>
       </c>
     </row>
